--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,6 +1014,215 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122729041</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98244</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Perssonakullen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>489394</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6396522</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Solberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122729428</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57275</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Perssonakullen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>489405</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6396649</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Solberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Tidemalm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122729041</v>
+        <v>122729428</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>57369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,41 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489394</v>
+        <v>489405</v>
       </c>
       <c r="R5" t="n">
-        <v>6396522</v>
+        <v>6396649</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122729428</v>
+        <v>122729041</v>
       </c>
       <c r="B6" t="n">
-        <v>57275</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,46 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489405</v>
+        <v>489394</v>
       </c>
       <c r="R6" t="n">
-        <v>6396649</v>
+        <v>6396522</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122729428</v>
+        <v>122729041</v>
       </c>
       <c r="B5" t="n">
-        <v>57369</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1028,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489405</v>
+        <v>489394</v>
       </c>
       <c r="R5" t="n">
-        <v>6396649</v>
+        <v>6396522</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122729041</v>
+        <v>122729428</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>57369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1130,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489394</v>
+        <v>489405</v>
       </c>
       <c r="R6" t="n">
-        <v>6396522</v>
+        <v>6396649</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122729041</v>
+        <v>122729428</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>57369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,41 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489394</v>
+        <v>489405</v>
       </c>
       <c r="R5" t="n">
-        <v>6396522</v>
+        <v>6396649</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122729428</v>
+        <v>122729041</v>
       </c>
       <c r="B6" t="n">
-        <v>57369</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,46 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489405</v>
+        <v>489394</v>
       </c>
       <c r="R6" t="n">
-        <v>6396649</v>
+        <v>6396522</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>122729041</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122729428</v>
+        <v>122729041</v>
       </c>
       <c r="B5" t="n">
-        <v>57369</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1028,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489405</v>
+        <v>489394</v>
       </c>
       <c r="R5" t="n">
-        <v>6396649</v>
+        <v>6396522</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122729041</v>
+        <v>122729428</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>57369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1130,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489394</v>
+        <v>489405</v>
       </c>
       <c r="R6" t="n">
-        <v>6396522</v>
+        <v>6396649</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>122729041</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122729041</v>
+        <v>122729428</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,41 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489394</v>
+        <v>489405</v>
       </c>
       <c r="R5" t="n">
-        <v>6396522</v>
+        <v>6396649</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122729428</v>
+        <v>122729041</v>
       </c>
       <c r="B6" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,46 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489405</v>
+        <v>489394</v>
       </c>
       <c r="R6" t="n">
-        <v>6396649</v>
+        <v>6396522</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>122729428</v>
       </c>
       <c r="B5" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>122729041</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 34063-2020 artfynd.xlsx
+++ b/artfynd/A 34063-2020 artfynd.xlsx
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122729428</v>
+        <v>122729041</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1028,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489405</v>
+        <v>489394</v>
       </c>
       <c r="R5" t="n">
-        <v>6396649</v>
+        <v>6396522</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122729041</v>
+        <v>122729428</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,41 +1130,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Perssonakullen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489394</v>
+        <v>489405</v>
       </c>
       <c r="R6" t="n">
-        <v>6396522</v>
+        <v>6396649</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
